--- a/data/trans_dic/IP21B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -736,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 80,85</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 77,36</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 63,88</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 56,83</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 80,72</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22,85; 100</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0; 56,93</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 64,98</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 50,86</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 33,19</t>
+          <t>3,71; 31,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 30,71</t>
+          <t>6,05; 31,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,77</t>
+          <t>0,0; 34,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,82</t>
+          <t>0,0; 67,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 24,95</t>
+          <t>2,75; 24,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 33,34</t>
+          <t>5,69; 31,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 42,45</t>
+          <t>5,01; 40,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 65,2</t>
+          <t>7,96; 63,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 22,42</t>
+          <t>5,89; 21,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 26,43</t>
+          <t>7,81; 26,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 30,58</t>
+          <t>5,77; 29,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 48,17</t>
+          <t>6,32; 47,41</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,27</t>
+          <t>0,0; 73,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 73,29</t>
+          <t>15,8; 68,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,32</t>
+          <t>0,0; 83,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 55,26</t>
+          <t>7,36; 58,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,35</t>
+          <t>0,0; 45,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,97</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 51,53</t>
+          <t>7,47; 51,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,02; 50,02</t>
+          <t>10,32; 50,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,11; 71,84</t>
+          <t>9,61; 73,07</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 21,69</t>
+          <t>2,68; 22,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 30,07</t>
+          <t>5,95; 30,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 39,94</t>
+          <t>9,79; 39,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 51,97</t>
+          <t>6,65; 52,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 22,93</t>
+          <t>4,41; 24,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 31,21</t>
+          <t>9,24; 30,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 40,87</t>
+          <t>9,39; 41,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 54,06</t>
+          <t>6,14; 52,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 19,07</t>
+          <t>5,67; 19,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 25,26</t>
+          <t>9,56; 25,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 33,65</t>
+          <t>12,76; 33,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 43,04</t>
+          <t>12,21; 45,42</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1567</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1897</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2710</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2462</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3303</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3010</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2788</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2469</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6616</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4317</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3098</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>630; 5431</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1303; 6695</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4158</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3670</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>674; 6081</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1215; 6666</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>735; 5919</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>618; 4947</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2445; 9030</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3350; 11274</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1547; 7881</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>835; 6267</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2920</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2346</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3224</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1138; 4963</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3151</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>584; 4654</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2331</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2590</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>920; 6311</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1274; 6225</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>610; 4635</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2469</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4777</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6538</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9171</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>681; 5737</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1669; 8673</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2078; 8339</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>613; 4824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1462; 8152</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3001; 9808</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1944; 8486</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>765; 6519</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3318; 11486</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5781; 15126</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5348; 14049</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2647; 9845</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Estudios-trans_dic.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,36</t>
+          <t>0,0; 80,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,88</t>
+          <t>0,0; 63,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,83</t>
+          <t>0,0; 56,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 31,99</t>
+          <t>3,72; 33,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 31,09</t>
+          <t>6,18; 34,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,27</t>
+          <t>0,0; 32,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,19</t>
+          <t>0,0; 62,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 24,82</t>
+          <t>2,91; 25,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,69; 31,21</t>
+          <t>5,63; 30,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 40,36</t>
+          <t>5,1; 40,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 63,77</t>
+          <t>8,29; 63,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 21,77</t>
+          <t>6,19; 22,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 26,28</t>
+          <t>7,8; 26,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 29,41</t>
+          <t>5,98; 31,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 47,41</t>
+          <t>6,69; 49,53</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,65</t>
+          <t>0,0; 73,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 68,93</t>
+          <t>10,03; 71,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,95</t>
+          <t>0,0; 81,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 58,66</t>
+          <t>7,7; 55,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,36</t>
+          <t>0,0; 56,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 83,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 51,26</t>
+          <t>5,51; 52,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 50,45</t>
+          <t>10,05; 49,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 73,07</t>
+          <t>10,31; 74,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 22,58</t>
+          <t>2,29; 20,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 30,95</t>
+          <t>5,56; 29,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,79; 39,28</t>
+          <t>10,16; 40,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 52,35</t>
+          <t>6,65; 51,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 24,59</t>
+          <t>5,66; 22,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 30,2</t>
+          <t>8,27; 30,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 41,0</t>
+          <t>7,71; 39,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 52,31</t>
+          <t>7,29; 55,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 19,61</t>
+          <t>5,66; 18,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 25,0</t>
+          <t>9,62; 25,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 33,51</t>
+          <t>12,56; 33,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 45,42</t>
+          <t>11,03; 45,71</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2462</t>
+          <t>0; 2561</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3303</t>
+          <t>0; 3293</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3010</t>
+          <t>0; 2982</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>630; 5431</t>
+          <t>631; 5633</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1303; 6695</t>
+          <t>1330; 7386</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4158</t>
+          <t>0; 3984</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3670</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>674; 6081</t>
+          <t>714; 6204</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1215; 6666</t>
+          <t>1203; 6583</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>735; 5919</t>
+          <t>748; 5998</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>618; 4947</t>
+          <t>643; 4956</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2445; 9030</t>
+          <t>2566; 9340</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3350; 11274</t>
+          <t>3344; 11187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1547; 7881</t>
+          <t>1604; 8323</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>835; 6267</t>
+          <t>884; 6547</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1925,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3224</t>
+          <t>0; 3202</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1138; 4963</t>
+          <t>722; 5150</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3151</t>
+          <t>0; 3051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1945,17 +1945,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>584; 4654</t>
+          <t>611; 4365</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2331</t>
+          <t>0; 2892</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2590</t>
+          <t>0; 2175</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>920; 6311</t>
+          <t>679; 6408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1274; 6225</t>
+          <t>1240; 6047</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>610; 4635</t>
+          <t>654; 4721</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>681; 5737</t>
+          <t>583; 5282</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1669; 8673</t>
+          <t>1559; 8175</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2078; 8339</t>
+          <t>2157; 8692</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>613; 4824</t>
+          <t>613; 4782</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1462; 8152</t>
+          <t>1877; 7536</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3001; 9808</t>
+          <t>2687; 9777</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1944; 8486</t>
+          <t>1597; 8186</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>765; 6519</t>
+          <t>908; 6874</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3318; 11486</t>
+          <t>3316; 11013</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5781; 15126</t>
+          <t>5821; 15389</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5348; 14049</t>
+          <t>5266; 14230</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2647; 9845</t>
+          <t>2390; 9907</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>39,86%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>35,63%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,52 +717,52 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 80,72</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 80,85</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 80,49</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,7</t>
+          <t>0,0; 64,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,29</t>
+          <t>0,0; 50,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32,35%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>14,55%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>15,93%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,24%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 33,18</t>
+          <t>2,79; 24,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 34,3</t>
+          <t>5,64; 33,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,84</t>
+          <t>5,18; 42,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,85</t>
+          <t>7,67; 68,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 25,32</t>
+          <t>3,76; 33,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 30,82</t>
+          <t>6,27; 30,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 40,9</t>
+          <t>0,0; 34,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 63,89</t>
+          <t>0,0; 65,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 22,52</t>
+          <t>5,98; 22,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 26,08</t>
+          <t>7,94; 26,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 31,06</t>
+          <t>7,31; 30,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 49,53</t>
+          <t>7,97; 52,22</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32,4%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>21,09%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37,85%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>40,91%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>35,72%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>23,71%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,16</t>
+          <t>7,18; 55,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 71,52</t>
+          <t>0,0; 46,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,29</t>
+          <t>0,0; 83,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,7; 55,02</t>
+          <t>0,0; 72,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,27</t>
+          <t>10,12; 73,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,97</t>
+          <t>0,0; 85,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 52,04</t>
+          <t>5,78; 51,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,05; 49,0</t>
+          <t>10,02; 50,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 74,43</t>
+          <t>10,47; 72,29</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,72%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 20,79</t>
+          <t>4,29; 22,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 29,17</t>
+          <t>8,1; 31,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 40,95</t>
+          <t>7,93; 40,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 51,89</t>
+          <t>7,75; 55,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 22,73</t>
+          <t>2,51; 21,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 30,1</t>
+          <t>5,22; 30,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 39,55</t>
+          <t>9,84; 39,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 55,16</t>
+          <t>7,54; 55,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 18,81</t>
+          <t>5,38; 19,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 25,44</t>
+          <t>9,75; 25,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 33,94</t>
+          <t>12,2; 33,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,03; 45,71</t>
+          <t>11,63; 44,95</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,32 +1368,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>676</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1504,52 +1504,52 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3352</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2569</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0; 1897</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2710</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2561</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3293</t>
+          <t>0; 3359</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2982</t>
+          <t>0; 2694</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2256</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2469</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3430</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1363</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2733</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3187</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2954</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>860</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3116</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>631; 5633</t>
+          <t>683; 6113</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1330; 7386</t>
+          <t>1204; 7122</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3984</t>
+          <t>759; 6225</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3433</t>
+          <t>535; 4802</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>714; 6204</t>
+          <t>639; 5635</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1203; 6583</t>
+          <t>1351; 6613</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>748; 5998</t>
+          <t>0; 4218</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>643; 4956</t>
+          <t>0; 3366</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2566; 9340</t>
+          <t>2481; 9298</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3344; 11187</t>
+          <t>3404; 11336</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1604; 8323</t>
+          <t>1958; 8196</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>884; 6547</t>
+          <t>968; 6344</t>
         </is>
       </c>
     </row>
@@ -1789,37 +1789,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1857,44 +1857,44 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2738</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1421</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>2920</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2240</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1925,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3202</t>
+          <t>570; 4384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>722; 5150</t>
+          <t>0; 2382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3051</t>
+          <t>0; 1905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1945,17 +1945,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>611; 4365</t>
+          <t>0; 3163</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2892</t>
+          <t>729; 5277</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2175</t>
+          <t>0; 3121</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>679; 6408</t>
+          <t>712; 6344</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1240; 6047</t>
+          <t>1236; 6172</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>654; 4721</t>
+          <t>623; 4302</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2469</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4353</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4777</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5356</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>583; 5282</t>
+          <t>1421; 7603</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1559; 8175</t>
+          <t>2630; 10136</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2157; 8692</t>
+          <t>1642; 8458</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>613; 4782</t>
+          <t>877; 6332</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1877; 7536</t>
+          <t>638; 5511</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2687; 9777</t>
+          <t>1463; 8427</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1597; 8186</t>
+          <t>2089; 8479</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>908; 6874</t>
+          <t>666; 4896</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3316; 11013</t>
+          <t>3148; 11170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5821; 15389</t>
+          <t>5902; 15280</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5266; 14230</t>
+          <t>5116; 14107</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2390; 9907</t>
+          <t>2344; 9061</t>
         </is>
       </c>
     </row>
